--- a/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/02_CMP2 - Risk, İş Sürekliliği ve Bilgi Sistemleri/EKG-YNT-PLN-05_acil_durum_reaksiyon_planlari_risk_bazinda.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/02_CMP2 - Risk, İş Sürekliliği ve Bilgi Sistemleri/EKG-YNT-PLN-05_acil_durum_reaksiyon_planlari_risk_bazinda.xlsx
@@ -999,7 +999,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-PLN-05&amp;C&amp;"Arial,Regular"&amp;11Acil Durum Reaksiyon Planları (risk bazında)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 01.09.2026
+Revizyon nedeni: Depremde korunma ve güvenli tahliye adımları eklendi; yangında yetkili müdahale sınırı netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R757bf613a31b4186"/>
   <x:tableParts count="1">
@@ -1363,7 +1364,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-PLN-05&amp;C&amp;"Arial,Regular"&amp;11Acil Durum Reaksiyon Planları (risk bazında)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 01.09.2026
+Revizyon nedeni: Depremde korunma ve güvenli tahliye adımları eklendi; yangında yetkili müdahale sınırı netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0ae9759eba54620"/>
   <x:tableParts count="1">
@@ -1702,7 +1704,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-PLN-05&amp;C&amp;"Arial,Regular"&amp;11Acil Durum Reaksiyon Planları (risk bazında)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 01.09.2026
+Revizyon nedeni: Depremde korunma ve güvenli tahliye adımları eklendi; yangında yetkili müdahale sınırı netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raed6067cd8604912"/>
   <x:tableParts count="1">
